--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rb07695387ba145fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R8fae3d36b56a4197"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -443,7 +443,7 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
-        <x:v>本次业务的脱敏隐私请求冻结快照、保留条款、删除窗口说明和起始SQL</x:v>
+        <x:v>本次业务输入中的隐私请求冻结快照、保留条款、删除窗口说明和起始SQL</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R8fae3d36b56a4197"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rccc20d714c6d4fc2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -446,25 +446,25 @@
         <x:v>本次业务输入中的隐私请求冻结快照、保留条款、删除窗口说明和起始SQL</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="48" customHeight="1">
+    <x:row r="6" ht="63" customHeight="1">
       <x:c r="A6" s="16" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>原始输入文件</x:v>
       </x:c>
       <x:c r="B6" s="17" t="str">
-        <x:v>解压输入数据包，读取input_data下的数据库、JSON、window目录与starter目录</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="63" customHeight="1">
+        <x:v>privacy_request.db；retention_exceptions.json；window/deletion_window.json；starter/rebuild_privacy_window.sql</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="33" customHeight="1">
       <x:c r="A7" s="16" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>窗口目标</x:v>
       </x:c>
       <x:c r="B7" s="17" t="str">
-        <x:v>privacy_request.db；retention_exceptions.json；window/deletion_window.json；starter/rebuild_privacy_window.sql</x:v>
+        <x:v>为开放状态删除请求编排逐对象动作，登记保留责任，并形成可供审批的窗口结论</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="63" customHeight="1">
       <x:c r="A8" s="16" t="str">
-        <x:v>目标输出文件</x:v>
+        <x:v>交付文件</x:v>
       </x:c>
       <x:c r="B8" s="17" t="str">
         <x:v>privacy_window.db；rebuild_privacy_window.sql；object_actions.csv；retention_register.csv；window_decision.json</x:v>
@@ -472,90 +472,90 @@
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="16" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>请求范围合同</x:v>
       </x:c>
       <x:c r="B9" s="17" t="str">
-        <x:v>识别开放删除请求；载入保留条款；展开五类对象；按优先级确定动作；建立登记与汇总；导出业务材料；形成窗口结论</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="48" customHeight="1">
+        <x:v>只处理request_type为delete且status为open的请求，覆盖对应用户的users、devices、orders、messages和audit_events对象</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="33" customHeight="1">
       <x:c r="A10" s="16" t="str">
-        <x:v>请求范围合同</x:v>
+        <x:v>例外优先级合同</x:v>
       </x:c>
       <x:c r="B10" s="17" t="str">
-        <x:v>只处理request_type为delete且status为open的请求，覆盖对应用户的users、devices、orders、messages和audit_events对象</x:v>
+        <x:v>法务保全优先；再判断订单税务留存与审计事件风控留存；不受例外约束的用户资料匿名化，其余对象删除</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="33" customHeight="1">
       <x:c r="A11" s="16" t="str">
-        <x:v>例外优先级合同</x:v>
+        <x:v>对象动作合同</x:v>
       </x:c>
       <x:c r="B11" s="17" t="str">
-        <x:v>法务保全优先；再判断订单税务留存与审计事件风控留存；不受例外约束的用户资料匿名化，其余对象删除</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="33" customHeight="1">
+        <x:v>每个范围内对象恰有一行，包含请求、用户、对象身份、对象时间、状态、计划动作、例外编号和动作依据</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="48" customHeight="1">
       <x:c r="A12" s="16" t="str">
-        <x:v>对象动作合同</x:v>
+        <x:v>保留登记合同</x:v>
       </x:c>
       <x:c r="B12" s="17" t="str">
-        <x:v>每个范围内对象恰有一行，包含请求、用户、对象身份、对象时间、状态、计划动作、例外编号和动作依据</x:v>
+        <x:v>只登记retain_exception对象，成员与对象动作的保留子集相同，原因和截止日期来自同一例外规则</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
       <x:c r="A13" s="16" t="str">
-        <x:v>保留登记合同</x:v>
+        <x:v>冻结快照合同</x:v>
       </x:c>
       <x:c r="B13" s="17" t="str">
-        <x:v>只登记retain_exception对象，成员与对象动作的保留子集相同，原因和截止日期来自同一例外规则</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="48" customHeight="1">
+        <x:v>结果数据库保留users、privacy_requests、devices、orders、messages和audit_events六张源表的原值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="33" customHeight="1">
       <x:c r="A14" s="16" t="str">
-        <x:v>冻结快照合同</x:v>
+        <x:v>窗口汇总合同</x:v>
       </x:c>
       <x:c r="B14" s="17" t="str">
-        <x:v>结果数据库保留users、privacy_requests、devices、orders、messages和audit_events六张源表的原值</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="33" customHeight="1">
+        <x:v>按metric、value两列记录开放删除请求、动作、例外、受影响用户和保留规则的可复算数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="48" customHeight="1">
       <x:c r="A15" s="16" t="str">
-        <x:v>窗口汇总合同</x:v>
+        <x:v>窗口结论合同</x:v>
       </x:c>
       <x:c r="B15" s="17" t="str">
-        <x:v>按metric、value两列记录开放删除请求、动作、例外、受影响用户和保留规则的可复算数量</x:v>
+        <x:v>关联窗口说明、规则生效日期、规则编号与全部汇总；业务关系闭合时进入READY_FOR_APPROVAL</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
       <x:c r="A16" s="16" t="str">
-        <x:v>窗口结论合同</x:v>
+        <x:v>SQLite步骤</x:v>
       </x:c>
       <x:c r="B16" s="17" t="str">
-        <x:v>关联窗口说明、规则生效日期、规则编号与全部汇总；业务关系闭合时进入READY_FOR_APPROVAL</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="48" customHeight="1">
+        <x:v>读取冻结数据库与JSON条款，筛选请求范围，按优先级写入对象动作和保留登记，再由汇总表导出两份报告与窗口结论</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="33" customHeight="1">
       <x:c r="A17" s="16" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>交付用途</x:v>
       </x:c>
       <x:c r="B17" s="17" t="str">
-        <x:v>入口正常结束，全部声明交付可读，删除请求范围、例外优先级、对象动作、保留登记、汇总和窗口结论相互一致</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="48" customHeight="1">
+        <x:v>数据平台值班使用对象动作安排处理顺序，合规复核人核对保留责任，隐私运营负责人依据窗口结论审批</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="33" customHeight="1">
       <x:c r="A18" s="16" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>结果对账</x:v>
       </x:c>
       <x:c r="B18" s="17" t="str">
-        <x:v>SQLite表结构；源表内容；请求集合；对象动作；例外编号；保留集合；两份CSV；汇总值；窗口字段与结论</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="33" customHeight="1">
+        <x:v>对象动作覆盖请求范围，保留登记等于对象动作中的保留子集，汇总和窗口结论可回到业务表与窗口说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="48" customHeight="1">
       <x:c r="A19" s="18" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B19" s="19" t="str">
-        <x:v>SQL等价组织、SQLite页布局、CSV行尾、无业务顺序的记录排列、JSON键序和等义动作依据</x:v>
+        <x:v>允许调整SQL组织、SQLite页布局、CSV行尾、无业务顺序记录排列、JSON键序和动作依据表述；业务主键、规则优先级、动作枚举与交付路径保持不变</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rccc20d714c6d4fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rf8cc13a1be074c98"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -443,7 +443,7 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
-        <x:v>本次业务输入中的隐私请求冻结快照、保留条款、删除窗口说明和起始SQL</x:v>
+        <x:v>本次业务输入中的材料说明、隐私请求冻结快照、保留条款、删除窗口说明和起始SQL</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="63" customHeight="1">
@@ -451,7 +451,7 @@
         <x:v>原始输入文件</x:v>
       </x:c>
       <x:c r="B6" s="17" t="str">
-        <x:v>privacy_request.db；retention_exceptions.json；window/deletion_window.json；starter/rebuild_privacy_window.sql</x:v>
+        <x:v>README.md；privacy_request.db；retention_exceptions.json；window/deletion_window.json；starter/rebuild_privacy_window.sql</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="33" customHeight="1">

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rf8cc13a1be074c98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R96d24806fe724954"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -443,7 +443,7 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="17" t="str">
-        <x:v>本次业务输入中的材料说明、隐私请求冻结快照、保留条款、删除窗口说明和起始SQL</x:v>
+        <x:v>本次业务输入中的材料说明、隐私请求数据库、保留条款、删除窗口说明和起始SQL</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="63" customHeight="1">
@@ -504,7 +504,7 @@
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
       <x:c r="A13" s="16" t="str">
-        <x:v>冻结快照合同</x:v>
+        <x:v>源表保全</x:v>
       </x:c>
       <x:c r="B13" s="17" t="str">
         <x:v>结果数据库保留users、privacy_requests、devices、orders、messages和audit_events六张源表的原值</x:v>
@@ -512,50 +512,50 @@
     </x:row>
     <x:row r="14" ht="33" customHeight="1">
       <x:c r="A14" s="16" t="str">
-        <x:v>窗口汇总合同</x:v>
+        <x:v>窗口汇总</x:v>
       </x:c>
       <x:c r="B14" s="17" t="str">
-        <x:v>按metric、value两列记录开放删除请求、动作、例外、受影响用户和保留规则的可复算数量</x:v>
+        <x:v>按metric、value两列记录开放删除请求、动作、例外、受影响用户和保留规则数量</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
       <x:c r="A15" s="16" t="str">
-        <x:v>窗口结论合同</x:v>
+        <x:v>审批材料</x:v>
       </x:c>
       <x:c r="B15" s="17" t="str">
-        <x:v>关联窗口说明、规则生效日期、规则编号与全部汇总；业务关系闭合时进入READY_FOR_APPROVAL</x:v>
+        <x:v>窗口结论关联窗口说明、规则生效日期、当前规则编号和业务汇总；对象动作与保留责任闭合时进入READY_FOR_APPROVAL</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
       <x:c r="A16" s="16" t="str">
-        <x:v>SQLite步骤</x:v>
+        <x:v>SQLite处理链</x:v>
       </x:c>
       <x:c r="B16" s="17" t="str">
-        <x:v>读取冻结数据库与JSON条款，筛选请求范围，按优先级写入对象动作和保留登记，再由汇总表导出两份报告与窗口结论</x:v>
+        <x:v>读取业务数据库与JSON条款，筛选请求范围，按优先级写入对象动作和保留登记，再从汇总表导出两份报告与窗口结论</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="33" customHeight="1">
       <x:c r="A17" s="16" t="str">
-        <x:v>交付用途</x:v>
+        <x:v>数据平台值班</x:v>
       </x:c>
       <x:c r="B17" s="17" t="str">
-        <x:v>数据平台值班使用对象动作安排处理顺序，合规复核人核对保留责任，隐私运营负责人依据窗口结论审批</x:v>
+        <x:v>使用object_actions.csv安排删除、匿名化和保留动作的处理顺序</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="33" customHeight="1">
       <x:c r="A18" s="16" t="str">
-        <x:v>结果对账</x:v>
+        <x:v>合规复核</x:v>
       </x:c>
       <x:c r="B18" s="17" t="str">
-        <x:v>对象动作覆盖请求范围，保留登记等于对象动作中的保留子集，汇总和窗口结论可回到业务表与窗口说明</x:v>
+        <x:v>使用retention_register.csv核对每个保留对象的条款、原因和截止日期</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
       <x:c r="A19" s="18" t="str">
-        <x:v>实现边界</x:v>
+        <x:v>隐私运营审批</x:v>
       </x:c>
       <x:c r="B19" s="19" t="str">
-        <x:v>允许调整SQL组织、SQLite页布局、CSV行尾、无业务顺序记录排列、JSON键序和动作依据表述；业务主键、规则优先级、动作枚举与交付路径保持不变</x:v>
+        <x:v>使用window_decision.json核对窗口时间、审批角色、规则编号和汇总后决定是否进入审批</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
